--- a/RC_data.xlsx
+++ b/RC_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -497,6 +497,80 @@
         </is>
       </c>
       <c r="G2" t="inlineStr">
+        <is>
+          <t>$550.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>#  9650362</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Corona, CA</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Encinitas, CA</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  01/10/2025</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SCM Express Inc  </t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ryland Vann </t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>$550.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>#  9650362</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Corona, CA</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Encinitas, CA</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  01/10/2025</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SCM Express Inc  </t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ryland Vann </t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>$550.00</t>
         </is>
